--- a/output/yearly_population_iteration_28_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_28_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5267</v>
+        <v>5831</v>
       </c>
       <c r="C2" t="n">
-        <v>11145</v>
+        <v>9972</v>
       </c>
       <c r="D2" t="n">
-        <v>29956</v>
+        <v>35093</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4173</v>
+        <v>3363</v>
       </c>
       <c r="C3" t="n">
-        <v>11070</v>
+        <v>6082</v>
       </c>
       <c r="D3" t="n">
-        <v>16488</v>
+        <v>19369</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3459</v>
+        <v>2762</v>
       </c>
       <c r="C4" t="n">
-        <v>7556</v>
+        <v>4223</v>
       </c>
       <c r="D4" t="n">
-        <v>7607</v>
+        <v>8768</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2055</v>
+        <v>1863</v>
       </c>
       <c r="C5" t="n">
-        <v>5727</v>
+        <v>3940</v>
       </c>
       <c r="D5" t="n">
-        <v>2812</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="6">
@@ -839,10 +839,10 @@
         <v>1099</v>
       </c>
       <c r="C6" t="n">
-        <v>4027</v>
+        <v>2599</v>
       </c>
       <c r="D6" t="n">
-        <v>1164</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C7" t="n">
-        <v>2717</v>
+        <v>1443</v>
       </c>
       <c r="D7" t="n">
-        <v>643</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C8" t="n">
-        <v>1324</v>
+        <v>623</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>503</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7369</v>
+        <v>7017</v>
       </c>
       <c r="C2" t="n">
-        <v>7807</v>
+        <v>7891</v>
       </c>
       <c r="D2" t="n">
-        <v>27412</v>
+        <v>39299</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3805</v>
+        <v>3621</v>
       </c>
       <c r="C3" t="n">
-        <v>9857</v>
+        <v>6908</v>
       </c>
       <c r="D3" t="n">
-        <v>17048</v>
+        <v>20205</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3237</v>
+        <v>2591</v>
       </c>
       <c r="C4" t="n">
-        <v>8844</v>
+        <v>4986</v>
       </c>
       <c r="D4" t="n">
-        <v>8581</v>
+        <v>10147</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2295</v>
+        <v>2014</v>
       </c>
       <c r="C5" t="n">
-        <v>6380</v>
+        <v>3991</v>
       </c>
       <c r="D5" t="n">
-        <v>3416</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1334</v>
+        <v>1300</v>
       </c>
       <c r="C6" t="n">
-        <v>4637</v>
+        <v>3153</v>
       </c>
       <c r="D6" t="n">
-        <v>1358</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>655</v>
+        <v>678</v>
       </c>
       <c r="C7" t="n">
-        <v>3215</v>
+        <v>1963</v>
       </c>
       <c r="D7" t="n">
-        <v>707</v>
+        <v>743</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="C8" t="n">
-        <v>1869</v>
+        <v>970</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C9" t="n">
-        <v>803</v>
+        <v>438</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>322</v>
+        <v>245</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8174</v>
+        <v>8677</v>
       </c>
       <c r="C2" t="n">
-        <v>11651</v>
+        <v>6954</v>
       </c>
       <c r="D2" t="n">
-        <v>23942</v>
+        <v>44041</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4143</v>
+        <v>4045</v>
       </c>
       <c r="C3" t="n">
-        <v>8143</v>
+        <v>6484</v>
       </c>
       <c r="D3" t="n">
-        <v>17144</v>
+        <v>21323</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2950</v>
+        <v>2563</v>
       </c>
       <c r="C4" t="n">
-        <v>9058</v>
+        <v>5731</v>
       </c>
       <c r="D4" t="n">
-        <v>9458</v>
+        <v>11383</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2352</v>
+        <v>2007</v>
       </c>
       <c r="C5" t="n">
-        <v>7108</v>
+        <v>4289</v>
       </c>
       <c r="D5" t="n">
-        <v>3923</v>
+        <v>4671</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1541</v>
+        <v>1450</v>
       </c>
       <c r="C6" t="n">
-        <v>5190</v>
+        <v>3439</v>
       </c>
       <c r="D6" t="n">
-        <v>1584</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>799</v>
+        <v>840</v>
       </c>
       <c r="C7" t="n">
-        <v>3697</v>
+        <v>2452</v>
       </c>
       <c r="D7" t="n">
-        <v>782</v>
+        <v>828</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="C8" t="n">
-        <v>2343</v>
+        <v>1349</v>
       </c>
       <c r="D8" t="n">
-        <v>467</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="C9" t="n">
-        <v>1150</v>
+        <v>636</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>474</v>
+        <v>316</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7606</v>
+        <v>7812</v>
       </c>
       <c r="C2" t="n">
-        <v>8388</v>
+        <v>4728</v>
       </c>
       <c r="D2" t="n">
-        <v>20141</v>
+        <v>36051</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4984</v>
+        <v>4768</v>
       </c>
       <c r="C3" t="n">
-        <v>12836</v>
+        <v>9369</v>
       </c>
       <c r="D3" t="n">
-        <v>18467</v>
+        <v>23148</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2173</v>
+        <v>1854</v>
       </c>
       <c r="C4" t="n">
-        <v>11432</v>
+        <v>7308</v>
       </c>
       <c r="D4" t="n">
-        <v>8832</v>
+        <v>10659</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1423</v>
+        <v>1339</v>
       </c>
       <c r="C5" t="n">
-        <v>5086</v>
+        <v>3370</v>
       </c>
       <c r="D5" t="n">
-        <v>2569</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>738</v>
+        <v>776</v>
       </c>
       <c r="C6" t="n">
-        <v>3623</v>
+        <v>2402</v>
       </c>
       <c r="D6" t="n">
-        <v>766</v>
+        <v>811</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="C7" t="n">
-        <v>2296</v>
+        <v>1322</v>
       </c>
       <c r="D7" t="n">
-        <v>457</v>
+        <v>487</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>1127</v>
+        <v>623</v>
       </c>
       <c r="D8" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>464</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="D10" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4644</v>
+        <v>4907</v>
       </c>
       <c r="C2" t="n">
-        <v>4299</v>
+        <v>2306</v>
       </c>
       <c r="D2" t="n">
-        <v>14242</v>
+        <v>24724</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5181</v>
+        <v>5180</v>
       </c>
       <c r="C3" t="n">
-        <v>9998</v>
+        <v>6606</v>
       </c>
       <c r="D3" t="n">
-        <v>17824</v>
+        <v>23569</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2760</v>
+        <v>2565</v>
       </c>
       <c r="C4" t="n">
-        <v>12239</v>
+        <v>8316</v>
       </c>
       <c r="D4" t="n">
-        <v>9943</v>
+        <v>12457</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1590</v>
+        <v>1471</v>
       </c>
       <c r="C5" t="n">
-        <v>7600</v>
+        <v>5087</v>
       </c>
       <c r="D5" t="n">
-        <v>3261</v>
+        <v>3947</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>855</v>
+        <v>913</v>
       </c>
       <c r="C6" t="n">
-        <v>4260</v>
+        <v>2859</v>
       </c>
       <c r="D6" t="n">
-        <v>935</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="C7" t="n">
-        <v>2787</v>
+        <v>1734</v>
       </c>
       <c r="D7" t="n">
-        <v>500</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>1469</v>
+        <v>833</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>471</v>
+        <v>353</v>
       </c>
       <c r="D9" t="n">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5199</v>
+        <v>4527</v>
       </c>
       <c r="C2" t="n">
-        <v>5404</v>
+        <v>5208</v>
       </c>
       <c r="D2" t="n">
-        <v>11328</v>
+        <v>29685</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4185</v>
+        <v>4291</v>
       </c>
       <c r="C3" t="n">
-        <v>6737</v>
+        <v>4066</v>
       </c>
       <c r="D3" t="n">
-        <v>16196</v>
+        <v>22340</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3182</v>
+        <v>3142</v>
       </c>
       <c r="C4" t="n">
-        <v>10973</v>
+        <v>7305</v>
       </c>
       <c r="D4" t="n">
-        <v>10851</v>
+        <v>13891</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1830</v>
+        <v>1722</v>
       </c>
       <c r="C5" t="n">
-        <v>9445</v>
+        <v>6500</v>
       </c>
       <c r="D5" t="n">
-        <v>4124</v>
+        <v>5134</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1037</v>
+        <v>1062</v>
       </c>
       <c r="C6" t="n">
-        <v>5600</v>
+        <v>3864</v>
       </c>
       <c r="D6" t="n">
-        <v>1235</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>439</v>
+        <v>487</v>
       </c>
       <c r="C7" t="n">
-        <v>3405</v>
+        <v>2235</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="C8" t="n">
-        <v>1973</v>
+        <v>1202</v>
       </c>
       <c r="D8" t="n">
-        <v>342</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>817</v>
+        <v>535</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>309</v>
+        <v>269</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3226</v>
+        <v>2694</v>
       </c>
       <c r="C2" t="n">
-        <v>2695</v>
+        <v>2458</v>
       </c>
       <c r="D2" t="n">
-        <v>8022</v>
+        <v>20713</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4248</v>
+        <v>4194</v>
       </c>
       <c r="C3" t="n">
-        <v>6170</v>
+        <v>4326</v>
       </c>
       <c r="D3" t="n">
-        <v>15391</v>
+        <v>22603</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3456</v>
+        <v>3507</v>
       </c>
       <c r="C4" t="n">
-        <v>10578</v>
+        <v>6797</v>
       </c>
       <c r="D4" t="n">
-        <v>11531</v>
+        <v>14914</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1867</v>
+        <v>1822</v>
       </c>
       <c r="C5" t="n">
-        <v>11275</v>
+        <v>7660</v>
       </c>
       <c r="D5" t="n">
-        <v>4233</v>
+        <v>5434</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>798</v>
+        <v>881</v>
       </c>
       <c r="C6" t="n">
-        <v>6376</v>
+        <v>4610</v>
       </c>
       <c r="D6" t="n">
-        <v>1205</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="C7" t="n">
-        <v>3527</v>
+        <v>2302</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1342</v>
+        <v>889</v>
       </c>
       <c r="D8" t="n">
-        <v>363</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>263</v>
       </c>
       <c r="D9" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3546</v>
+        <v>3599</v>
       </c>
       <c r="C2" t="n">
-        <v>4747</v>
+        <v>2539</v>
       </c>
       <c r="D2" t="n">
-        <v>11907</v>
+        <v>20603</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3297</v>
+        <v>3063</v>
       </c>
       <c r="C3" t="n">
-        <v>4211</v>
+        <v>3101</v>
       </c>
       <c r="D3" t="n">
-        <v>13585</v>
+        <v>21044</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3275</v>
+        <v>3305</v>
       </c>
       <c r="C4" t="n">
-        <v>8512</v>
+        <v>5558</v>
       </c>
       <c r="D4" t="n">
-        <v>11736</v>
+        <v>15641</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2196</v>
+        <v>2220</v>
       </c>
       <c r="C5" t="n">
-        <v>10860</v>
+        <v>7119</v>
       </c>
       <c r="D5" t="n">
-        <v>5085</v>
+        <v>6633</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1060</v>
+        <v>1132</v>
       </c>
       <c r="C6" t="n">
-        <v>8266</v>
+        <v>5946</v>
       </c>
       <c r="D6" t="n">
-        <v>1567</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>275</v>
+        <v>330</v>
       </c>
       <c r="C7" t="n">
-        <v>4593</v>
+        <v>3228</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>695</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>2095</v>
+        <v>1418</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>616</v>
+        <v>473</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
         <v>133</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2483</v>
+        <v>2560</v>
       </c>
       <c r="C2" t="n">
-        <v>2930</v>
+        <v>2603</v>
       </c>
       <c r="D2" t="n">
-        <v>8729</v>
+        <v>15081</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2958</v>
+        <v>2834</v>
       </c>
       <c r="C3" t="n">
-        <v>4063</v>
+        <v>2640</v>
       </c>
       <c r="D3" t="n">
-        <v>12810</v>
+        <v>19846</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3018</v>
+        <v>2979</v>
       </c>
       <c r="C4" t="n">
-        <v>6929</v>
+        <v>4611</v>
       </c>
       <c r="D4" t="n">
-        <v>11704</v>
+        <v>16191</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2356</v>
+        <v>2404</v>
       </c>
       <c r="C5" t="n">
-        <v>10284</v>
+        <v>6621</v>
       </c>
       <c r="D5" t="n">
-        <v>5617</v>
+        <v>7446</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1210</v>
+        <v>1337</v>
       </c>
       <c r="C6" t="n">
-        <v>9318</v>
+        <v>6557</v>
       </c>
       <c r="D6" t="n">
-        <v>1864</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="C7" t="n">
-        <v>5617</v>
+        <v>4114</v>
       </c>
       <c r="D7" t="n">
-        <v>688</v>
+        <v>780</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>2645</v>
+        <v>1849</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>648</v>
+        <v>555</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3730</v>
+        <v>4011</v>
       </c>
       <c r="C2" t="n">
-        <v>12981</v>
+        <v>4839</v>
       </c>
       <c r="D2" t="n">
-        <v>10122</v>
+        <v>18676</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2363</v>
+        <v>2303</v>
       </c>
       <c r="C3" t="n">
-        <v>3262</v>
+        <v>2356</v>
       </c>
       <c r="D3" t="n">
-        <v>11553</v>
+        <v>18004</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2605</v>
+        <v>2544</v>
       </c>
       <c r="C4" t="n">
-        <v>5656</v>
+        <v>3682</v>
       </c>
       <c r="D4" t="n">
-        <v>11496</v>
+        <v>16225</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2364</v>
+        <v>2395</v>
       </c>
       <c r="C5" t="n">
-        <v>8813</v>
+        <v>5672</v>
       </c>
       <c r="D5" t="n">
-        <v>6205</v>
+        <v>8394</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1436</v>
+        <v>1578</v>
       </c>
       <c r="C6" t="n">
-        <v>9588</v>
+        <v>6526</v>
       </c>
       <c r="D6" t="n">
-        <v>2272</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>465</v>
+        <v>551</v>
       </c>
       <c r="C7" t="n">
-        <v>6884</v>
+        <v>5022</v>
       </c>
       <c r="D7" t="n">
-        <v>807</v>
+        <v>950</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>3631</v>
+        <v>2665</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1241</v>
+        <v>978</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>39</v>
+      </c>
+      <c r="D14" t="n">
         <v>37</v>
-      </c>
-      <c r="D14" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6658</v>
+        <v>4828</v>
       </c>
       <c r="C2" t="n">
-        <v>15149</v>
+        <v>4376</v>
       </c>
       <c r="D2" t="n">
-        <v>15544</v>
+        <v>8747</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2755</v>
+        <v>2869</v>
       </c>
       <c r="C2" t="n">
-        <v>7789</v>
+        <v>2748</v>
       </c>
       <c r="D2" t="n">
-        <v>7612</v>
+        <v>13746</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3161</v>
+        <v>3117</v>
       </c>
       <c r="C3" t="n">
-        <v>5617</v>
+        <v>3135</v>
       </c>
       <c r="D3" t="n">
-        <v>12459</v>
+        <v>19569</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3493</v>
+        <v>3512</v>
       </c>
       <c r="C4" t="n">
-        <v>8586</v>
+        <v>5525</v>
       </c>
       <c r="D4" t="n">
-        <v>11702</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1326</v>
+        <v>1524</v>
       </c>
       <c r="C5" t="n">
-        <v>13213</v>
+        <v>8819</v>
       </c>
       <c r="D5" t="n">
-        <v>5543</v>
+        <v>7498</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>429</v>
+        <v>509</v>
       </c>
       <c r="C6" t="n">
-        <v>8343</v>
+        <v>6200</v>
       </c>
       <c r="D6" t="n">
-        <v>1786</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>3558</v>
+        <v>2611</v>
       </c>
       <c r="D7" t="n">
-        <v>497</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1216</v>
+        <v>958</v>
       </c>
       <c r="D8" t="n">
-        <v>279</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>38</v>
+      </c>
+      <c r="D13" t="n">
         <v>36</v>
-      </c>
-      <c r="D13" t="n">
-        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7764</v>
+        <v>7423</v>
       </c>
       <c r="C2" t="n">
-        <v>9801</v>
+        <v>3711</v>
       </c>
       <c r="D2" t="n">
-        <v>16047</v>
+        <v>19898</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2828</v>
+        <v>2052</v>
       </c>
       <c r="C3" t="n">
-        <v>7635</v>
+        <v>2240</v>
       </c>
       <c r="D3" t="n">
-        <v>3250</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
         <v>154</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5377</v>
+        <v>6062</v>
       </c>
       <c r="C2" t="n">
-        <v>6386</v>
+        <v>5819</v>
       </c>
       <c r="D2" t="n">
-        <v>17035</v>
+        <v>25467</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4348</v>
+        <v>3885</v>
       </c>
       <c r="C3" t="n">
-        <v>7641</v>
+        <v>2679</v>
       </c>
       <c r="D3" t="n">
-        <v>5160</v>
+        <v>4941</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1263</v>
+        <v>925</v>
       </c>
       <c r="C4" t="n">
-        <v>4517</v>
+        <v>1355</v>
       </c>
       <c r="D4" t="n">
-        <v>1836</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4963,10 +4963,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4980,10 +4980,10 @@
         <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6506</v>
+        <v>5672</v>
       </c>
       <c r="C2" t="n">
-        <v>8094</v>
+        <v>8551</v>
       </c>
       <c r="D2" t="n">
-        <v>29175</v>
+        <v>28300</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3991</v>
+        <v>4064</v>
       </c>
       <c r="C3" t="n">
-        <v>6043</v>
+        <v>3801</v>
       </c>
       <c r="D3" t="n">
-        <v>6688</v>
+        <v>7869</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2348</v>
+        <v>2031</v>
       </c>
       <c r="C4" t="n">
-        <v>6162</v>
+        <v>2076</v>
       </c>
       <c r="D4" t="n">
-        <v>2418</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>570</v>
+        <v>440</v>
       </c>
       <c r="C5" t="n">
-        <v>2527</v>
+        <v>834</v>
       </c>
       <c r="D5" t="n">
-        <v>1277</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6553</v>
+        <v>5091</v>
       </c>
       <c r="C2" t="n">
-        <v>8217</v>
+        <v>5038</v>
       </c>
       <c r="D2" t="n">
-        <v>28926</v>
+        <v>29611</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4212</v>
+        <v>3967</v>
       </c>
       <c r="C3" t="n">
-        <v>6165</v>
+        <v>5436</v>
       </c>
       <c r="D3" t="n">
-        <v>9465</v>
+        <v>10420</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2650</v>
+        <v>2579</v>
       </c>
       <c r="C4" t="n">
-        <v>5912</v>
+        <v>2940</v>
       </c>
       <c r="D4" t="n">
-        <v>3059</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1185</v>
+        <v>1006</v>
       </c>
       <c r="C5" t="n">
-        <v>4323</v>
+        <v>1472</v>
       </c>
       <c r="D5" t="n">
-        <v>1435</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>301</v>
+        <v>256</v>
       </c>
       <c r="C6" t="n">
-        <v>1390</v>
+        <v>569</v>
       </c>
       <c r="D6" t="n">
-        <v>938</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8972</v>
+        <v>6299</v>
       </c>
       <c r="C2" t="n">
-        <v>13525</v>
+        <v>7755</v>
       </c>
       <c r="D2" t="n">
-        <v>36031</v>
+        <v>33986</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3843</v>
+        <v>3329</v>
       </c>
       <c r="C3" t="n">
-        <v>5884</v>
+        <v>4286</v>
       </c>
       <c r="D3" t="n">
-        <v>10915</v>
+        <v>11857</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2085</v>
+        <v>2017</v>
       </c>
       <c r="C4" t="n">
-        <v>4940</v>
+        <v>3513</v>
       </c>
       <c r="D4" t="n">
-        <v>3523</v>
+        <v>3792</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>989</v>
+        <v>926</v>
       </c>
       <c r="C5" t="n">
-        <v>3694</v>
+        <v>1644</v>
       </c>
       <c r="D5" t="n">
-        <v>1354</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>338</v>
+        <v>300</v>
       </c>
       <c r="C6" t="n">
-        <v>1891</v>
+        <v>686</v>
       </c>
       <c r="D6" t="n">
-        <v>767</v>
+        <v>775</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>533</v>
+        <v>294</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7166</v>
+        <v>5128</v>
       </c>
       <c r="C2" t="n">
-        <v>10781</v>
+        <v>3888</v>
       </c>
       <c r="D2" t="n">
-        <v>26858</v>
+        <v>39350</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5225</v>
+        <v>4003</v>
       </c>
       <c r="C3" t="n">
-        <v>8859</v>
+        <v>5451</v>
       </c>
       <c r="D3" t="n">
-        <v>14435</v>
+        <v>14860</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2543</v>
+        <v>2345</v>
       </c>
       <c r="C4" t="n">
-        <v>5333</v>
+        <v>3914</v>
       </c>
       <c r="D4" t="n">
-        <v>4801</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1354</v>
+        <v>1304</v>
       </c>
       <c r="C5" t="n">
-        <v>4322</v>
+        <v>2722</v>
       </c>
       <c r="D5" t="n">
-        <v>1729</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>598</v>
+        <v>571</v>
       </c>
       <c r="C6" t="n">
-        <v>2855</v>
+        <v>1229</v>
       </c>
       <c r="D6" t="n">
-        <v>855</v>
+        <v>863</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="C7" t="n">
-        <v>1264</v>
+        <v>516</v>
       </c>
       <c r="D7" t="n">
         <v>559</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>262</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5007</v>
+        <v>4452</v>
       </c>
       <c r="C2" t="n">
-        <v>17391</v>
+        <v>9917</v>
       </c>
       <c r="D2" t="n">
-        <v>31559</v>
+        <v>36839</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5041</v>
+        <v>3749</v>
       </c>
       <c r="C3" t="n">
-        <v>8570</v>
+        <v>3980</v>
       </c>
       <c r="D3" t="n">
-        <v>15307</v>
+        <v>17708</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3239</v>
+        <v>2710</v>
       </c>
       <c r="C4" t="n">
-        <v>7032</v>
+        <v>4703</v>
       </c>
       <c r="D4" t="n">
-        <v>6412</v>
+        <v>7036</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1688</v>
+        <v>1609</v>
       </c>
       <c r="C5" t="n">
-        <v>4756</v>
+        <v>3291</v>
       </c>
       <c r="D5" t="n">
-        <v>2190</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>858</v>
+        <v>844</v>
       </c>
       <c r="C6" t="n">
-        <v>3556</v>
+        <v>2017</v>
       </c>
       <c r="D6" t="n">
-        <v>994</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C7" t="n">
-        <v>2030</v>
+        <v>893</v>
       </c>
       <c r="D7" t="n">
-        <v>597</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>804</v>
+        <v>391</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>285</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_28_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_28_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5831</v>
+        <v>6530</v>
       </c>
       <c r="C2" t="n">
-        <v>9972</v>
+        <v>12776</v>
       </c>
       <c r="D2" t="n">
-        <v>35093</v>
+        <v>26645</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3363</v>
+        <v>3704</v>
       </c>
       <c r="C3" t="n">
-        <v>6082</v>
+        <v>4488</v>
       </c>
       <c r="D3" t="n">
-        <v>19369</v>
+        <v>18590</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2762</v>
+        <v>2852</v>
       </c>
       <c r="C4" t="n">
-        <v>4223</v>
+        <v>4855</v>
       </c>
       <c r="D4" t="n">
-        <v>8768</v>
+        <v>9235</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1863</v>
+        <v>1836</v>
       </c>
       <c r="C5" t="n">
-        <v>3940</v>
+        <v>4339</v>
       </c>
       <c r="D5" t="n">
-        <v>3104</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1099</v>
+        <v>1003</v>
       </c>
       <c r="C6" t="n">
-        <v>2599</v>
+        <v>3022</v>
       </c>
       <c r="D6" t="n">
-        <v>1215</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>502</v>
+        <v>449</v>
       </c>
       <c r="C7" t="n">
-        <v>1443</v>
+        <v>1746</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C8" t="n">
-        <v>623</v>
+        <v>808</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -881,10 +881,10 @@
         <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7017</v>
+        <v>7884</v>
       </c>
       <c r="C2" t="n">
-        <v>7891</v>
+        <v>13782</v>
       </c>
       <c r="D2" t="n">
-        <v>39299</v>
+        <v>36741</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3621</v>
+        <v>4003</v>
       </c>
       <c r="C3" t="n">
-        <v>6908</v>
+        <v>7205</v>
       </c>
       <c r="D3" t="n">
-        <v>20205</v>
+        <v>18436</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2591</v>
+        <v>2776</v>
       </c>
       <c r="C4" t="n">
-        <v>4986</v>
+        <v>4581</v>
       </c>
       <c r="D4" t="n">
-        <v>10147</v>
+        <v>10480</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2014</v>
+        <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>3991</v>
+        <v>4439</v>
       </c>
       <c r="D5" t="n">
-        <v>3934</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1300</v>
+        <v>1228</v>
       </c>
       <c r="C6" t="n">
-        <v>3153</v>
+        <v>3544</v>
       </c>
       <c r="D6" t="n">
-        <v>1476</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>678</v>
+        <v>608</v>
       </c>
       <c r="C7" t="n">
-        <v>1963</v>
+        <v>2308</v>
       </c>
       <c r="D7" t="n">
-        <v>743</v>
+        <v>761</v>
       </c>
     </row>
     <row r="8">
@@ -1175,10 +1175,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>280</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>970</v>
+        <v>1195</v>
       </c>
       <c r="D8" t="n">
         <v>464</v>
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C9" t="n">
-        <v>438</v>
+        <v>540</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -1206,7 +1206,7 @@
         <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
         <v>250</v>
@@ -1223,7 +1223,7 @@
         <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8677</v>
+        <v>8256</v>
       </c>
       <c r="C2" t="n">
-        <v>6954</v>
+        <v>9961</v>
       </c>
       <c r="D2" t="n">
-        <v>44041</v>
+        <v>29618</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4045</v>
+        <v>4482</v>
       </c>
       <c r="C3" t="n">
-        <v>6484</v>
+        <v>8724</v>
       </c>
       <c r="D3" t="n">
-        <v>21323</v>
+        <v>19452</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2563</v>
+        <v>2775</v>
       </c>
       <c r="C4" t="n">
-        <v>5731</v>
+        <v>5550</v>
       </c>
       <c r="D4" t="n">
-        <v>11383</v>
+        <v>11206</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2007</v>
+        <v>2052</v>
       </c>
       <c r="C5" t="n">
-        <v>4289</v>
+        <v>4362</v>
       </c>
       <c r="D5" t="n">
-        <v>4671</v>
+        <v>5045</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1450</v>
+        <v>1406</v>
       </c>
       <c r="C6" t="n">
-        <v>3439</v>
+        <v>3873</v>
       </c>
       <c r="D6" t="n">
-        <v>1810</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>840</v>
+        <v>756</v>
       </c>
       <c r="C7" t="n">
-        <v>2452</v>
+        <v>2768</v>
       </c>
       <c r="D7" t="n">
-        <v>828</v>
+        <v>877</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>382</v>
+        <v>341</v>
       </c>
       <c r="C8" t="n">
-        <v>1349</v>
+        <v>1608</v>
       </c>
       <c r="D8" t="n">
-        <v>497</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C9" t="n">
-        <v>636</v>
+        <v>783</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>316</v>
+        <v>359</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7812</v>
+        <v>7606</v>
       </c>
       <c r="C2" t="n">
-        <v>4728</v>
+        <v>6853</v>
       </c>
       <c r="D2" t="n">
-        <v>36051</v>
+        <v>24628</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4768</v>
+        <v>5190</v>
       </c>
       <c r="C3" t="n">
-        <v>9369</v>
+        <v>11834</v>
       </c>
       <c r="D3" t="n">
-        <v>23148</v>
+        <v>21182</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1854</v>
+        <v>1896</v>
       </c>
       <c r="C4" t="n">
-        <v>7308</v>
+        <v>7171</v>
       </c>
       <c r="D4" t="n">
-        <v>10659</v>
+        <v>10802</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1339</v>
+        <v>1299</v>
       </c>
       <c r="C5" t="n">
-        <v>3370</v>
+        <v>3795</v>
       </c>
       <c r="D5" t="n">
-        <v>3029</v>
+        <v>3296</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>776</v>
+        <v>698</v>
       </c>
       <c r="C6" t="n">
-        <v>2402</v>
+        <v>2712</v>
       </c>
       <c r="D6" t="n">
-        <v>811</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352</v>
+        <v>315</v>
       </c>
       <c r="C7" t="n">
-        <v>1322</v>
+        <v>1575</v>
       </c>
       <c r="D7" t="n">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>623</v>
+        <v>767</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>351</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4907</v>
+        <v>4560</v>
       </c>
       <c r="C2" t="n">
-        <v>2306</v>
+        <v>4146</v>
       </c>
       <c r="D2" t="n">
-        <v>24724</v>
+        <v>17286</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5180</v>
+        <v>5396</v>
       </c>
       <c r="C3" t="n">
-        <v>6606</v>
+        <v>8817</v>
       </c>
       <c r="D3" t="n">
-        <v>23569</v>
+        <v>20633</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2565</v>
+        <v>2686</v>
       </c>
       <c r="C4" t="n">
-        <v>8316</v>
+        <v>9332</v>
       </c>
       <c r="D4" t="n">
-        <v>12457</v>
+        <v>12072</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1471</v>
+        <v>1431</v>
       </c>
       <c r="C5" t="n">
-        <v>5087</v>
+        <v>5259</v>
       </c>
       <c r="D5" t="n">
-        <v>3947</v>
+        <v>4195</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>913</v>
+        <v>835</v>
       </c>
       <c r="C6" t="n">
-        <v>2859</v>
+        <v>3215</v>
       </c>
       <c r="D6" t="n">
-        <v>1037</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>331</v>
+        <v>294</v>
       </c>
       <c r="C7" t="n">
-        <v>1734</v>
+        <v>2014</v>
       </c>
       <c r="D7" t="n">
-        <v>532</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>833</v>
+        <v>1003</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>396</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4527</v>
+        <v>5106</v>
       </c>
       <c r="C2" t="n">
-        <v>5208</v>
+        <v>5461</v>
       </c>
       <c r="D2" t="n">
-        <v>29685</v>
+        <v>16083</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4291</v>
+        <v>4244</v>
       </c>
       <c r="C3" t="n">
-        <v>4066</v>
+        <v>5923</v>
       </c>
       <c r="D3" t="n">
-        <v>22340</v>
+        <v>18791</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3142</v>
+        <v>3303</v>
       </c>
       <c r="C4" t="n">
-        <v>7305</v>
+        <v>8890</v>
       </c>
       <c r="D4" t="n">
-        <v>13891</v>
+        <v>13102</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1722</v>
+        <v>1729</v>
       </c>
       <c r="C5" t="n">
-        <v>6500</v>
+        <v>7026</v>
       </c>
       <c r="D5" t="n">
-        <v>5134</v>
+        <v>5277</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1062</v>
+        <v>987</v>
       </c>
       <c r="C6" t="n">
-        <v>3864</v>
+        <v>4118</v>
       </c>
       <c r="D6" t="n">
-        <v>1442</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>487</v>
+        <v>442</v>
       </c>
       <c r="C7" t="n">
-        <v>2235</v>
+        <v>2539</v>
       </c>
       <c r="D7" t="n">
-        <v>595</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C8" t="n">
-        <v>1202</v>
+        <v>1408</v>
       </c>
       <c r="D8" t="n">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>535</v>
+        <v>619</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2694</v>
+        <v>3056</v>
       </c>
       <c r="C2" t="n">
-        <v>2458</v>
+        <v>2609</v>
       </c>
       <c r="D2" t="n">
-        <v>20713</v>
+        <v>11231</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4194</v>
+        <v>4289</v>
       </c>
       <c r="C3" t="n">
-        <v>4326</v>
+        <v>5600</v>
       </c>
       <c r="D3" t="n">
-        <v>22603</v>
+        <v>18088</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3507</v>
+        <v>3619</v>
       </c>
       <c r="C4" t="n">
-        <v>6797</v>
+        <v>8618</v>
       </c>
       <c r="D4" t="n">
-        <v>14914</v>
+        <v>13874</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1822</v>
+        <v>1781</v>
       </c>
       <c r="C5" t="n">
-        <v>7660</v>
+        <v>8442</v>
       </c>
       <c r="D5" t="n">
-        <v>5434</v>
+        <v>5559</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>881</v>
+        <v>800</v>
       </c>
       <c r="C6" t="n">
-        <v>4610</v>
+        <v>4951</v>
       </c>
       <c r="D6" t="n">
-        <v>1403</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>2302</v>
+        <v>2632</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>889</v>
+        <v>1020</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3599</v>
+        <v>3244</v>
       </c>
       <c r="C2" t="n">
-        <v>2539</v>
+        <v>7481</v>
       </c>
       <c r="D2" t="n">
-        <v>20603</v>
+        <v>15060</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3063</v>
+        <v>3243</v>
       </c>
       <c r="C3" t="n">
-        <v>3101</v>
+        <v>3818</v>
       </c>
       <c r="D3" t="n">
-        <v>21044</v>
+        <v>16113</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3305</v>
+        <v>3392</v>
       </c>
       <c r="C4" t="n">
-        <v>5558</v>
+        <v>7048</v>
       </c>
       <c r="D4" t="n">
-        <v>15641</v>
+        <v>14099</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2220</v>
+        <v>2214</v>
       </c>
       <c r="C5" t="n">
-        <v>7119</v>
+        <v>8425</v>
       </c>
       <c r="D5" t="n">
-        <v>6633</v>
+        <v>6587</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1132</v>
+        <v>1057</v>
       </c>
       <c r="C6" t="n">
-        <v>5946</v>
+        <v>6396</v>
       </c>
       <c r="D6" t="n">
-        <v>1926</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>330</v>
+        <v>292</v>
       </c>
       <c r="C7" t="n">
-        <v>3228</v>
+        <v>3591</v>
       </c>
       <c r="D7" t="n">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1418</v>
+        <v>1608</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>473</v>
+        <v>518</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
         <v>175</v>
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
+        <v>129</v>
+      </c>
+      <c r="D11" t="n">
         <v>134</v>
-      </c>
-      <c r="D11" t="n">
-        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>58</v>
+      </c>
+      <c r="D13" t="n">
         <v>60</v>
-      </c>
-      <c r="D13" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2560</v>
+        <v>2386</v>
       </c>
       <c r="C2" t="n">
-        <v>2603</v>
+        <v>4945</v>
       </c>
       <c r="D2" t="n">
-        <v>15081</v>
+        <v>12375</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2834</v>
+        <v>2844</v>
       </c>
       <c r="C3" t="n">
-        <v>2640</v>
+        <v>4795</v>
       </c>
       <c r="D3" t="n">
-        <v>19846</v>
+        <v>15264</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2979</v>
+        <v>3084</v>
       </c>
       <c r="C4" t="n">
-        <v>4611</v>
+        <v>5833</v>
       </c>
       <c r="D4" t="n">
-        <v>16191</v>
+        <v>14057</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2404</v>
+        <v>2407</v>
       </c>
       <c r="C5" t="n">
-        <v>6621</v>
+        <v>8016</v>
       </c>
       <c r="D5" t="n">
-        <v>7446</v>
+        <v>7306</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1337</v>
+        <v>1246</v>
       </c>
       <c r="C6" t="n">
-        <v>6557</v>
+        <v>7271</v>
       </c>
       <c r="D6" t="n">
-        <v>2366</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>297</v>
+        <v>262</v>
       </c>
       <c r="C7" t="n">
-        <v>4114</v>
+        <v>4495</v>
       </c>
       <c r="D7" t="n">
-        <v>780</v>
+        <v>784</v>
       </c>
     </row>
     <row r="8">
@@ -3352,10 +3352,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1849</v>
+        <v>2071</v>
       </c>
       <c r="D8" t="n">
         <v>413</v>
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>555</v>
+        <v>588</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4011</v>
+        <v>3144</v>
       </c>
       <c r="C2" t="n">
-        <v>4839</v>
+        <v>7925</v>
       </c>
       <c r="D2" t="n">
-        <v>18676</v>
+        <v>11832</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2303</v>
+        <v>2262</v>
       </c>
       <c r="C3" t="n">
-        <v>2356</v>
+        <v>4324</v>
       </c>
       <c r="D3" t="n">
-        <v>18004</v>
+        <v>14086</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2544</v>
+        <v>2634</v>
       </c>
       <c r="C4" t="n">
-        <v>3682</v>
+        <v>5283</v>
       </c>
       <c r="D4" t="n">
-        <v>16225</v>
+        <v>13656</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="C5" t="n">
-        <v>5672</v>
+        <v>6990</v>
       </c>
       <c r="D5" t="n">
-        <v>8394</v>
+        <v>7991</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1578</v>
+        <v>1507</v>
       </c>
       <c r="C6" t="n">
-        <v>6526</v>
+        <v>7490</v>
       </c>
       <c r="D6" t="n">
-        <v>2969</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>551</v>
+        <v>494</v>
       </c>
       <c r="C7" t="n">
-        <v>5022</v>
+        <v>5499</v>
       </c>
       <c r="D7" t="n">
-        <v>950</v>
+        <v>966</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>2665</v>
+        <v>2921</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>978</v>
+        <v>1058</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>138</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4828</v>
+        <v>5650</v>
       </c>
       <c r="C2" t="n">
-        <v>4376</v>
+        <v>6721</v>
       </c>
       <c r="D2" t="n">
-        <v>8747</v>
+        <v>18595</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2869</v>
+        <v>2275</v>
       </c>
       <c r="C2" t="n">
-        <v>2748</v>
+        <v>4629</v>
       </c>
       <c r="D2" t="n">
-        <v>13746</v>
+        <v>8803</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3117</v>
+        <v>3053</v>
       </c>
       <c r="C3" t="n">
-        <v>3135</v>
+        <v>5489</v>
       </c>
       <c r="D3" t="n">
-        <v>19569</v>
+        <v>15102</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3512</v>
+        <v>3539</v>
       </c>
       <c r="C4" t="n">
-        <v>5525</v>
+        <v>7726</v>
       </c>
       <c r="D4" t="n">
-        <v>16500</v>
+        <v>14109</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1524</v>
+        <v>1436</v>
       </c>
       <c r="C5" t="n">
-        <v>8819</v>
+        <v>10374</v>
       </c>
       <c r="D5" t="n">
-        <v>7498</v>
+        <v>7243</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>509</v>
+        <v>456</v>
       </c>
       <c r="C6" t="n">
-        <v>6200</v>
+        <v>6783</v>
       </c>
       <c r="D6" t="n">
-        <v>2264</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>2611</v>
+        <v>2862</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>958</v>
+        <v>1036</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
         <v>135</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7423</v>
+        <v>6307</v>
       </c>
       <c r="C2" t="n">
-        <v>3711</v>
+        <v>5978</v>
       </c>
       <c r="D2" t="n">
-        <v>19898</v>
+        <v>22459</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2052</v>
+        <v>2401</v>
       </c>
       <c r="C3" t="n">
-        <v>2240</v>
+        <v>3387</v>
       </c>
       <c r="D3" t="n">
-        <v>2108</v>
+        <v>3763</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6062</v>
+        <v>4498</v>
       </c>
       <c r="C2" t="n">
-        <v>5819</v>
+        <v>4762</v>
       </c>
       <c r="D2" t="n">
-        <v>25467</v>
+        <v>23045</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3885</v>
+        <v>3575</v>
       </c>
       <c r="C3" t="n">
-        <v>2679</v>
+        <v>4185</v>
       </c>
       <c r="D3" t="n">
-        <v>4941</v>
+        <v>6626</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>925</v>
+        <v>1077</v>
       </c>
       <c r="C4" t="n">
-        <v>1355</v>
+        <v>2029</v>
       </c>
       <c r="D4" t="n">
-        <v>1606</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5672</v>
+        <v>4801</v>
       </c>
       <c r="C2" t="n">
-        <v>8551</v>
+        <v>9206</v>
       </c>
       <c r="D2" t="n">
-        <v>28300</v>
+        <v>35364</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4064</v>
+        <v>3316</v>
       </c>
       <c r="C3" t="n">
-        <v>3801</v>
+        <v>3894</v>
       </c>
       <c r="D3" t="n">
-        <v>7869</v>
+        <v>8775</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2031</v>
+        <v>1978</v>
       </c>
       <c r="C4" t="n">
-        <v>2076</v>
+        <v>3207</v>
       </c>
       <c r="D4" t="n">
-        <v>2197</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>440</v>
+        <v>493</v>
       </c>
       <c r="C5" t="n">
-        <v>834</v>
+        <v>1207</v>
       </c>
       <c r="D5" t="n">
-        <v>1215</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5091</v>
+        <v>7027</v>
       </c>
       <c r="C2" t="n">
-        <v>5038</v>
+        <v>7205</v>
       </c>
       <c r="D2" t="n">
-        <v>29611</v>
+        <v>33921</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3967</v>
+        <v>3292</v>
       </c>
       <c r="C3" t="n">
-        <v>5436</v>
+        <v>5769</v>
       </c>
       <c r="D3" t="n">
-        <v>10420</v>
+        <v>12198</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2579</v>
+        <v>2226</v>
       </c>
       <c r="C4" t="n">
-        <v>2940</v>
+        <v>3509</v>
       </c>
       <c r="D4" t="n">
-        <v>3143</v>
+        <v>3788</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1006</v>
+        <v>1018</v>
       </c>
       <c r="C5" t="n">
-        <v>1472</v>
+        <v>2218</v>
       </c>
       <c r="D5" t="n">
-        <v>1357</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="C6" t="n">
-        <v>569</v>
+        <v>748</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6299</v>
+        <v>6524</v>
       </c>
       <c r="C2" t="n">
-        <v>7755</v>
+        <v>7089</v>
       </c>
       <c r="D2" t="n">
-        <v>33986</v>
+        <v>32259</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3329</v>
+        <v>3695</v>
       </c>
       <c r="C3" t="n">
-        <v>4286</v>
+        <v>5319</v>
       </c>
       <c r="D3" t="n">
-        <v>11857</v>
+        <v>13774</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2017</v>
+        <v>1713</v>
       </c>
       <c r="C4" t="n">
-        <v>3513</v>
+        <v>3845</v>
       </c>
       <c r="D4" t="n">
-        <v>3792</v>
+        <v>4544</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>926</v>
+        <v>839</v>
       </c>
       <c r="C5" t="n">
-        <v>1644</v>
+        <v>2107</v>
       </c>
       <c r="D5" t="n">
-        <v>1331</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C6" t="n">
-        <v>686</v>
+        <v>988</v>
       </c>
       <c r="D6" t="n">
-        <v>775</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5128</v>
+        <v>5534</v>
       </c>
       <c r="C2" t="n">
-        <v>3888</v>
+        <v>6047</v>
       </c>
       <c r="D2" t="n">
-        <v>39350</v>
+        <v>33399</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4003</v>
+        <v>4225</v>
       </c>
       <c r="C3" t="n">
-        <v>5451</v>
+        <v>5462</v>
       </c>
       <c r="D3" t="n">
-        <v>14860</v>
+        <v>15865</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2345</v>
+        <v>2352</v>
       </c>
       <c r="C4" t="n">
-        <v>3914</v>
+        <v>4656</v>
       </c>
       <c r="D4" t="n">
-        <v>5380</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1304</v>
+        <v>1139</v>
       </c>
       <c r="C5" t="n">
-        <v>2722</v>
+        <v>3080</v>
       </c>
       <c r="D5" t="n">
-        <v>1786</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>571</v>
+        <v>528</v>
       </c>
       <c r="C6" t="n">
-        <v>1229</v>
+        <v>1609</v>
       </c>
       <c r="D6" t="n">
-        <v>863</v>
+        <v>918</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C7" t="n">
-        <v>516</v>
+        <v>705</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4452</v>
+        <v>4995</v>
       </c>
       <c r="C2" t="n">
-        <v>9917</v>
+        <v>5256</v>
       </c>
       <c r="D2" t="n">
-        <v>36839</v>
+        <v>33281</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3749</v>
+        <v>3996</v>
       </c>
       <c r="C3" t="n">
-        <v>3980</v>
+        <v>5008</v>
       </c>
       <c r="D3" t="n">
-        <v>17708</v>
+        <v>17528</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2710</v>
+        <v>2789</v>
       </c>
       <c r="C4" t="n">
-        <v>4703</v>
+        <v>5007</v>
       </c>
       <c r="D4" t="n">
-        <v>7036</v>
+        <v>7885</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1609</v>
+        <v>1520</v>
       </c>
       <c r="C5" t="n">
-        <v>3291</v>
+        <v>3833</v>
       </c>
       <c r="D5" t="n">
-        <v>2370</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>844</v>
+        <v>746</v>
       </c>
       <c r="C6" t="n">
-        <v>2017</v>
+        <v>2367</v>
       </c>
       <c r="D6" t="n">
-        <v>1019</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="C7" t="n">
-        <v>893</v>
+        <v>1174</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>391</v>
+        <v>496</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_28_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_28_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6530</v>
+        <v>1421</v>
       </c>
       <c r="C2" t="n">
-        <v>12776</v>
+        <v>1688</v>
       </c>
       <c r="D2" t="n">
-        <v>26645</v>
+        <v>21705</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3704</v>
+        <v>2187</v>
       </c>
       <c r="C3" t="n">
-        <v>4488</v>
+        <v>4422</v>
       </c>
       <c r="D3" t="n">
-        <v>18590</v>
+        <v>17106</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2852</v>
+        <v>1385</v>
       </c>
       <c r="C4" t="n">
-        <v>4855</v>
+        <v>6158</v>
       </c>
       <c r="D4" t="n">
-        <v>9235</v>
+        <v>6188</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1836</v>
+        <v>692</v>
       </c>
       <c r="C5" t="n">
-        <v>4339</v>
+        <v>4124</v>
       </c>
       <c r="D5" t="n">
-        <v>3553</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1003</v>
+        <v>295</v>
       </c>
       <c r="C6" t="n">
-        <v>3022</v>
+        <v>1634</v>
       </c>
       <c r="D6" t="n">
-        <v>1347</v>
+        <v>737</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>449</v>
+        <v>104</v>
       </c>
       <c r="C7" t="n">
-        <v>1746</v>
+        <v>624</v>
       </c>
       <c r="D7" t="n">
-        <v>676</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>808</v>
+        <v>345</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7884</v>
+        <v>1173</v>
       </c>
       <c r="C2" t="n">
-        <v>13782</v>
+        <v>5701</v>
       </c>
       <c r="D2" t="n">
-        <v>36741</v>
+        <v>19749</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4003</v>
+        <v>1533</v>
       </c>
       <c r="C3" t="n">
-        <v>7205</v>
+        <v>2579</v>
       </c>
       <c r="D3" t="n">
-        <v>18436</v>
+        <v>16774</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2776</v>
+        <v>1536</v>
       </c>
       <c r="C4" t="n">
-        <v>4581</v>
+        <v>5122</v>
       </c>
       <c r="D4" t="n">
-        <v>10480</v>
+        <v>7991</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1999</v>
+        <v>896</v>
       </c>
       <c r="C5" t="n">
-        <v>4439</v>
+        <v>5112</v>
       </c>
       <c r="D5" t="n">
-        <v>4283</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1228</v>
+        <v>433</v>
       </c>
       <c r="C6" t="n">
-        <v>3544</v>
+        <v>2898</v>
       </c>
       <c r="D6" t="n">
-        <v>1667</v>
+        <v>924</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>608</v>
+        <v>165</v>
       </c>
       <c r="C7" t="n">
-        <v>2308</v>
+        <v>1124</v>
       </c>
       <c r="D7" t="n">
-        <v>761</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>1195</v>
+        <v>480</v>
       </c>
       <c r="D8" t="n">
-        <v>464</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>540</v>
+        <v>315</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8256</v>
+        <v>616</v>
       </c>
       <c r="C2" t="n">
-        <v>9961</v>
+        <v>2290</v>
       </c>
       <c r="D2" t="n">
-        <v>29618</v>
+        <v>13324</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4482</v>
+        <v>1373</v>
       </c>
       <c r="C3" t="n">
-        <v>8724</v>
+        <v>3716</v>
       </c>
       <c r="D3" t="n">
-        <v>19452</v>
+        <v>16698</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2775</v>
+        <v>1685</v>
       </c>
       <c r="C4" t="n">
-        <v>5550</v>
+        <v>4531</v>
       </c>
       <c r="D4" t="n">
-        <v>11206</v>
+        <v>9143</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2052</v>
+        <v>912</v>
       </c>
       <c r="C5" t="n">
-        <v>4362</v>
+        <v>5695</v>
       </c>
       <c r="D5" t="n">
-        <v>5045</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1406</v>
+        <v>350</v>
       </c>
       <c r="C6" t="n">
-        <v>3873</v>
+        <v>3764</v>
       </c>
       <c r="D6" t="n">
-        <v>1980</v>
+        <v>942</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>756</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>2768</v>
+        <v>1111</v>
       </c>
       <c r="D7" t="n">
-        <v>877</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>341</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1608</v>
+        <v>482</v>
       </c>
       <c r="D8" t="n">
-        <v>492</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>783</v>
+        <v>241</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>359</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7606</v>
+        <v>529</v>
       </c>
       <c r="C2" t="n">
-        <v>6853</v>
+        <v>2691</v>
       </c>
       <c r="D2" t="n">
-        <v>24628</v>
+        <v>16127</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5190</v>
+        <v>875</v>
       </c>
       <c r="C3" t="n">
-        <v>11834</v>
+        <v>2613</v>
       </c>
       <c r="D3" t="n">
-        <v>21182</v>
+        <v>15009</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1896</v>
+        <v>1373</v>
       </c>
       <c r="C4" t="n">
-        <v>7171</v>
+        <v>4042</v>
       </c>
       <c r="D4" t="n">
-        <v>10802</v>
+        <v>10243</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1299</v>
+        <v>1119</v>
       </c>
       <c r="C5" t="n">
-        <v>3795</v>
+        <v>5038</v>
       </c>
       <c r="D5" t="n">
-        <v>3296</v>
+        <v>4045</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>698</v>
+        <v>531</v>
       </c>
       <c r="C6" t="n">
-        <v>2712</v>
+        <v>4688</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>315</v>
+        <v>154</v>
       </c>
       <c r="C7" t="n">
-        <v>1575</v>
+        <v>2354</v>
       </c>
       <c r="D7" t="n">
-        <v>482</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4560</v>
+        <v>317</v>
       </c>
       <c r="C2" t="n">
-        <v>4146</v>
+        <v>1610</v>
       </c>
       <c r="D2" t="n">
-        <v>17286</v>
+        <v>11553</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5396</v>
+        <v>647</v>
       </c>
       <c r="C3" t="n">
-        <v>8817</v>
+        <v>2395</v>
       </c>
       <c r="D3" t="n">
-        <v>20633</v>
+        <v>14425</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2686</v>
+        <v>1106</v>
       </c>
       <c r="C4" t="n">
-        <v>9332</v>
+        <v>3388</v>
       </c>
       <c r="D4" t="n">
-        <v>12072</v>
+        <v>10762</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1431</v>
+        <v>1176</v>
       </c>
       <c r="C5" t="n">
-        <v>5259</v>
+        <v>4696</v>
       </c>
       <c r="D5" t="n">
-        <v>4195</v>
+        <v>4832</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>835</v>
+        <v>661</v>
       </c>
       <c r="C6" t="n">
-        <v>3215</v>
+        <v>5056</v>
       </c>
       <c r="D6" t="n">
-        <v>1116</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>294</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>2014</v>
+        <v>3223</v>
       </c>
       <c r="D7" t="n">
-        <v>527</v>
+        <v>684</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1003</v>
+        <v>1171</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>396</v>
+        <v>447</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5106</v>
+        <v>625</v>
       </c>
       <c r="C2" t="n">
-        <v>5461</v>
+        <v>8044</v>
       </c>
       <c r="D2" t="n">
-        <v>16083</v>
+        <v>13059</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4244</v>
+        <v>428</v>
       </c>
       <c r="C3" t="n">
-        <v>5923</v>
+        <v>1786</v>
       </c>
       <c r="D3" t="n">
-        <v>18791</v>
+        <v>13018</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3303</v>
+        <v>796</v>
       </c>
       <c r="C4" t="n">
-        <v>8890</v>
+        <v>2821</v>
       </c>
       <c r="D4" t="n">
-        <v>13102</v>
+        <v>11067</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1729</v>
+        <v>1061</v>
       </c>
       <c r="C5" t="n">
-        <v>7026</v>
+        <v>3970</v>
       </c>
       <c r="D5" t="n">
-        <v>5277</v>
+        <v>5652</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>987</v>
+        <v>805</v>
       </c>
       <c r="C6" t="n">
-        <v>4118</v>
+        <v>4889</v>
       </c>
       <c r="D6" t="n">
-        <v>1544</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>442</v>
+        <v>321</v>
       </c>
       <c r="C7" t="n">
-        <v>2539</v>
+        <v>4061</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>805</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>86</v>
       </c>
       <c r="C8" t="n">
-        <v>1408</v>
+        <v>2026</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>619</v>
+        <v>727</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3056</v>
+        <v>410</v>
       </c>
       <c r="C2" t="n">
-        <v>2609</v>
+        <v>4055</v>
       </c>
       <c r="D2" t="n">
-        <v>11231</v>
+        <v>9402</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4289</v>
+        <v>664</v>
       </c>
       <c r="C3" t="n">
-        <v>5600</v>
+        <v>3769</v>
       </c>
       <c r="D3" t="n">
-        <v>18088</v>
+        <v>13841</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3619</v>
+        <v>1360</v>
       </c>
       <c r="C4" t="n">
-        <v>8618</v>
+        <v>3986</v>
       </c>
       <c r="D4" t="n">
-        <v>13874</v>
+        <v>11518</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1781</v>
+        <v>832</v>
       </c>
       <c r="C5" t="n">
-        <v>8442</v>
+        <v>6355</v>
       </c>
       <c r="D5" t="n">
-        <v>5559</v>
+        <v>5191</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>800</v>
+        <v>296</v>
       </c>
       <c r="C6" t="n">
-        <v>4951</v>
+        <v>5273</v>
       </c>
       <c r="D6" t="n">
-        <v>1494</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="C7" t="n">
-        <v>2632</v>
+        <v>1985</v>
       </c>
       <c r="D7" t="n">
-        <v>595</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1020</v>
+        <v>712</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3244</v>
+        <v>214</v>
       </c>
       <c r="C2" t="n">
-        <v>7481</v>
+        <v>2334</v>
       </c>
       <c r="D2" t="n">
-        <v>15060</v>
+        <v>7908</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3243</v>
+        <v>471</v>
       </c>
       <c r="C3" t="n">
-        <v>3818</v>
+        <v>3472</v>
       </c>
       <c r="D3" t="n">
-        <v>16113</v>
+        <v>12154</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3392</v>
+        <v>871</v>
       </c>
       <c r="C4" t="n">
-        <v>7048</v>
+        <v>3643</v>
       </c>
       <c r="D4" t="n">
-        <v>14099</v>
+        <v>11224</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2214</v>
+        <v>764</v>
       </c>
       <c r="C5" t="n">
-        <v>8425</v>
+        <v>4623</v>
       </c>
       <c r="D5" t="n">
-        <v>6587</v>
+        <v>5455</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1057</v>
+        <v>299</v>
       </c>
       <c r="C6" t="n">
-        <v>6396</v>
+        <v>4792</v>
       </c>
       <c r="D6" t="n">
-        <v>2035</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>3591</v>
+        <v>2488</v>
       </c>
       <c r="D7" t="n">
-        <v>694</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1608</v>
+        <v>800</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>518</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>135</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2386</v>
+        <v>164</v>
       </c>
       <c r="C2" t="n">
-        <v>4945</v>
+        <v>3465</v>
       </c>
       <c r="D2" t="n">
-        <v>12375</v>
+        <v>11548</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2844</v>
+        <v>290</v>
       </c>
       <c r="C3" t="n">
-        <v>4795</v>
+        <v>2453</v>
       </c>
       <c r="D3" t="n">
-        <v>15264</v>
+        <v>10599</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3084</v>
+        <v>589</v>
       </c>
       <c r="C4" t="n">
-        <v>5833</v>
+        <v>3468</v>
       </c>
       <c r="D4" t="n">
-        <v>14057</v>
+        <v>11061</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2407</v>
+        <v>744</v>
       </c>
       <c r="C5" t="n">
-        <v>8016</v>
+        <v>4025</v>
       </c>
       <c r="D5" t="n">
-        <v>7306</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1246</v>
+        <v>473</v>
       </c>
       <c r="C6" t="n">
-        <v>7271</v>
+        <v>4695</v>
       </c>
       <c r="D6" t="n">
-        <v>2400</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>262</v>
+        <v>154</v>
       </c>
       <c r="C7" t="n">
-        <v>4495</v>
+        <v>3661</v>
       </c>
       <c r="D7" t="n">
-        <v>784</v>
+        <v>811</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>2071</v>
+        <v>1634</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>588</v>
+        <v>526</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3144</v>
+        <v>599</v>
       </c>
       <c r="C2" t="n">
-        <v>7925</v>
+        <v>6731</v>
       </c>
       <c r="D2" t="n">
-        <v>11832</v>
+        <v>14623</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2262</v>
+        <v>193</v>
       </c>
       <c r="C3" t="n">
-        <v>4324</v>
+        <v>2588</v>
       </c>
       <c r="D3" t="n">
-        <v>14086</v>
+        <v>9997</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2634</v>
+        <v>394</v>
       </c>
       <c r="C4" t="n">
-        <v>5283</v>
+        <v>2850</v>
       </c>
       <c r="D4" t="n">
-        <v>13656</v>
+        <v>10640</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2397</v>
+        <v>612</v>
       </c>
       <c r="C5" t="n">
-        <v>6990</v>
+        <v>3652</v>
       </c>
       <c r="D5" t="n">
-        <v>7991</v>
+        <v>6963</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1507</v>
+        <v>553</v>
       </c>
       <c r="C6" t="n">
-        <v>7490</v>
+        <v>4309</v>
       </c>
       <c r="D6" t="n">
-        <v>2981</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>494</v>
+        <v>265</v>
       </c>
       <c r="C7" t="n">
-        <v>5499</v>
+        <v>4166</v>
       </c>
       <c r="D7" t="n">
-        <v>966</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>2921</v>
+        <v>2586</v>
       </c>
       <c r="D8" t="n">
-        <v>448</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>1058</v>
+        <v>1025</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5650</v>
+        <v>4798</v>
       </c>
       <c r="C2" t="n">
-        <v>6721</v>
+        <v>7470</v>
       </c>
       <c r="D2" t="n">
-        <v>18595</v>
+        <v>10450</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2275</v>
+        <v>478</v>
       </c>
       <c r="C2" t="n">
-        <v>4629</v>
+        <v>5845</v>
       </c>
       <c r="D2" t="n">
-        <v>8803</v>
+        <v>20520</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3053</v>
+        <v>296</v>
       </c>
       <c r="C3" t="n">
-        <v>5489</v>
+        <v>3963</v>
       </c>
       <c r="D3" t="n">
-        <v>15102</v>
+        <v>9954</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3539</v>
+        <v>267</v>
       </c>
       <c r="C4" t="n">
-        <v>7726</v>
+        <v>2662</v>
       </c>
       <c r="D4" t="n">
-        <v>14109</v>
+        <v>10109</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1436</v>
+        <v>482</v>
       </c>
       <c r="C5" t="n">
-        <v>10374</v>
+        <v>3163</v>
       </c>
       <c r="D5" t="n">
-        <v>7243</v>
+        <v>7351</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>456</v>
+        <v>537</v>
       </c>
       <c r="C6" t="n">
-        <v>6783</v>
+        <v>3963</v>
       </c>
       <c r="D6" t="n">
-        <v>2255</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>350</v>
       </c>
       <c r="C7" t="n">
-        <v>2862</v>
+        <v>4228</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>1036</v>
+        <v>3266</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
-        <v>316</v>
+        <v>1657</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>614</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6307</v>
+        <v>3855</v>
       </c>
       <c r="C2" t="n">
-        <v>5978</v>
+        <v>7546</v>
       </c>
       <c r="D2" t="n">
-        <v>22459</v>
+        <v>18507</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2401</v>
+        <v>1585</v>
       </c>
       <c r="C3" t="n">
-        <v>3387</v>
+        <v>2949</v>
       </c>
       <c r="D3" t="n">
-        <v>3763</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4498</v>
+        <v>3660</v>
       </c>
       <c r="C2" t="n">
-        <v>4762</v>
+        <v>5772</v>
       </c>
       <c r="D2" t="n">
-        <v>23045</v>
+        <v>19029</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3575</v>
+        <v>2286</v>
       </c>
       <c r="C3" t="n">
-        <v>4185</v>
+        <v>4914</v>
       </c>
       <c r="D3" t="n">
-        <v>6626</v>
+        <v>4787</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1077</v>
+        <v>758</v>
       </c>
       <c r="C4" t="n">
-        <v>2029</v>
+        <v>1887</v>
       </c>
       <c r="D4" t="n">
-        <v>1939</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4801</v>
+        <v>2963</v>
       </c>
       <c r="C2" t="n">
-        <v>9206</v>
+        <v>5104</v>
       </c>
       <c r="D2" t="n">
-        <v>35364</v>
+        <v>17111</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3316</v>
+        <v>2457</v>
       </c>
       <c r="C3" t="n">
-        <v>3894</v>
+        <v>4654</v>
       </c>
       <c r="D3" t="n">
-        <v>8775</v>
+        <v>6827</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1978</v>
+        <v>1335</v>
       </c>
       <c r="C4" t="n">
-        <v>3207</v>
+        <v>3678</v>
       </c>
       <c r="D4" t="n">
-        <v>2779</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>493</v>
+        <v>370</v>
       </c>
       <c r="C5" t="n">
-        <v>1207</v>
+        <v>1186</v>
       </c>
       <c r="D5" t="n">
-        <v>1285</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>401</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>290</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7027</v>
+        <v>1885</v>
       </c>
       <c r="C2" t="n">
-        <v>7205</v>
+        <v>4906</v>
       </c>
       <c r="D2" t="n">
-        <v>33921</v>
+        <v>28373</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3292</v>
+        <v>2231</v>
       </c>
       <c r="C3" t="n">
-        <v>5769</v>
+        <v>4237</v>
       </c>
       <c r="D3" t="n">
-        <v>12198</v>
+        <v>7980</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2226</v>
+        <v>1638</v>
       </c>
       <c r="C4" t="n">
-        <v>3509</v>
+        <v>4163</v>
       </c>
       <c r="D4" t="n">
-        <v>3788</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1018</v>
+        <v>727</v>
       </c>
       <c r="C5" t="n">
-        <v>2218</v>
+        <v>2548</v>
       </c>
       <c r="D5" t="n">
-        <v>1491</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="C6" t="n">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="D6" t="n">
-        <v>960</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>311</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6524</v>
+        <v>1688</v>
       </c>
       <c r="C2" t="n">
-        <v>7089</v>
+        <v>4825</v>
       </c>
       <c r="D2" t="n">
-        <v>32259</v>
+        <v>39933</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3695</v>
+        <v>1716</v>
       </c>
       <c r="C3" t="n">
-        <v>5319</v>
+        <v>3986</v>
       </c>
       <c r="D3" t="n">
-        <v>13774</v>
+        <v>10517</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1713</v>
+        <v>1646</v>
       </c>
       <c r="C4" t="n">
-        <v>3845</v>
+        <v>4116</v>
       </c>
       <c r="D4" t="n">
-        <v>4544</v>
+        <v>3751</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>839</v>
+        <v>1018</v>
       </c>
       <c r="C5" t="n">
-        <v>2107</v>
+        <v>3347</v>
       </c>
       <c r="D5" t="n">
-        <v>1480</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>303</v>
+        <v>409</v>
       </c>
       <c r="C6" t="n">
-        <v>988</v>
+        <v>1658</v>
       </c>
       <c r="D6" t="n">
-        <v>799</v>
+        <v>901</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>349</v>
+        <v>523</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>299</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5534</v>
+        <v>3310</v>
       </c>
       <c r="C2" t="n">
-        <v>6047</v>
+        <v>6151</v>
       </c>
       <c r="D2" t="n">
-        <v>33399</v>
+        <v>40061</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4225</v>
+        <v>1426</v>
       </c>
       <c r="C3" t="n">
-        <v>5462</v>
+        <v>3844</v>
       </c>
       <c r="D3" t="n">
-        <v>15865</v>
+        <v>14029</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2352</v>
+        <v>1442</v>
       </c>
       <c r="C4" t="n">
-        <v>4656</v>
+        <v>3924</v>
       </c>
       <c r="D4" t="n">
-        <v>6223</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1139</v>
+        <v>1158</v>
       </c>
       <c r="C5" t="n">
-        <v>3080</v>
+        <v>3661</v>
       </c>
       <c r="D5" t="n">
-        <v>2052</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>528</v>
+        <v>612</v>
       </c>
       <c r="C6" t="n">
-        <v>1609</v>
+        <v>2451</v>
       </c>
       <c r="D6" t="n">
-        <v>918</v>
+        <v>991</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>177</v>
+        <v>233</v>
       </c>
       <c r="C7" t="n">
-        <v>705</v>
+        <v>1056</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>289</v>
+        <v>396</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4995</v>
+        <v>2866</v>
       </c>
       <c r="C2" t="n">
-        <v>5256</v>
+        <v>3789</v>
       </c>
       <c r="D2" t="n">
-        <v>33281</v>
+        <v>31356</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3996</v>
+        <v>2224</v>
       </c>
       <c r="C3" t="n">
-        <v>5008</v>
+        <v>6102</v>
       </c>
       <c r="D3" t="n">
-        <v>17528</v>
+        <v>15487</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2789</v>
+        <v>1069</v>
       </c>
       <c r="C4" t="n">
-        <v>5007</v>
+        <v>6000</v>
       </c>
       <c r="D4" t="n">
-        <v>7885</v>
+        <v>4486</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1520</v>
+        <v>565</v>
       </c>
       <c r="C5" t="n">
-        <v>3833</v>
+        <v>2401</v>
       </c>
       <c r="D5" t="n">
-        <v>2750</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>746</v>
+        <v>215</v>
       </c>
       <c r="C6" t="n">
-        <v>2367</v>
+        <v>1034</v>
       </c>
       <c r="D6" t="n">
-        <v>1092</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>1174</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>614</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>496</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
